--- a/WorkBot/main/data/order_archive/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/BALKAN BEVERAGE LLC/BALKAN BEVERAGE LLC_Collegetown_20260515.xlsx
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>24.95</v>
       </c>
       <c r="E6" t="n">
-        <v>49.9</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="7">
@@ -554,13 +554,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>42.85</v>
       </c>
       <c r="E9" t="n">
-        <v>85.7</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="10">
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>42.85</v>
       </c>
       <c r="E10" t="n">
-        <v>85.7</v>
+        <v>42.85</v>
       </c>
     </row>
   </sheetData>
